--- a/data/trans_dic/P21D_4_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21D_4_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,41</t>
+          <t>0,46; 2,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,47</t>
+          <t>0,3; 1,32</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,37</t>
+          <t>0,42; 2,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,53</t>
+          <t>0,36; 1,55</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,63</t>
+          <t>0,18; 1,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,2</t>
+          <t>0,13; 1,16</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,57</t>
+          <t>0,05; 0,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,08</t>
+          <t>0,41; 1,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,67</t>
+          <t>0,28; 0,7</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1776</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1328</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1527</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2704</t>
+          <t>0; 3554</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1270</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3503</t>
+          <t>0; 2861</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5238</t>
+          <t>0; 7205</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1165</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6024</t>
+          <t>0; 5966</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6416</t>
+          <t>0; 6589</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1553; 8169</t>
+          <t>1544; 8252</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2782; 11654</t>
+          <t>2385; 10492</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1719</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1845; 9853</t>
+          <t>1750; 10195</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2228; 9763</t>
+          <t>2268; 9895</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4140</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>580; 5178</t>
+          <t>580; 5160</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>570; 5306</t>
+          <t>588; 5117</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>874; 9284</t>
+          <t>838; 8313</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6134; 16700</t>
+          <t>6321; 16470</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8498; 21307</t>
+          <t>8917; 22207</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_4_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21D_4_R-Clase-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,44</t>
+          <t>0,47; 2,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,32</t>
+          <t>0,3; 1,34</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -777,19 +777,19 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,45</t>
+          <t>0,63; 2,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,55</t>
+          <t>0,38; 1,48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,62</t>
+          <t>0,15; 1,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,16</t>
+          <t>0,13; 1,04</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,51</t>
+          <t>0,06; 0,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,06</t>
+          <t>0,43; 1,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,7</t>
+          <t>0,31; 0,71</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3554</t>
+          <t>0; 3148</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2861</t>
+          <t>0; 2990</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7205</t>
+          <t>0; 4983</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5966</t>
+          <t>0; 4985</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>6385</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6589</t>
+          <t>0; 6011</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1544; 8252</t>
+          <t>1816; 8653</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2385; 10492</t>
+          <t>2685; 12051</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5242</t>
         </is>
       </c>
     </row>
@@ -1329,19 +1329,19 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1750; 10195</t>
+          <t>2445; 9764</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2268; 9895</t>
+          <t>2477; 9685</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2092</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>580; 5160</t>
+          <t>530; 5098</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>588; 5117</t>
+          <t>615; 4915</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14137</t>
+          <t>15300</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>838; 8313</t>
+          <t>990; 8525</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6321; 16470</t>
+          <t>7099; 18677</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8917; 22207</t>
+          <t>9976; 22514</t>
         </is>
       </c>
     </row>
